--- a/output/castle/growth/castle_growth_per_castle.xlsx
+++ b/output/castle/growth/castle_growth_per_castle.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -502,10 +502,10 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>1372123</v>
+        <v>1172123</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr"/>
@@ -531,19 +531,19 @@
         <v>1.37</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>45996</v>
+        <v>45992</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>$30007307475</t>
+          <t>.เปู่เสฉวน</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -552,21 +552,17 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1372123</v>
+        <v>1107702</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.11</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -584,61 +580,61 @@
       <c r="E5" s="5" t="n">
         <v>2.11</v>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>90.09999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>45995</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>.เปู่เสฉวน</t>
+          <t>amelix</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2107702</v>
+        <v>1137505</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.14</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>.เปู่เสฉวน</t>
+          <t>amelix</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2107702</v>
+        <v>1237505</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2.11</v>
+        <v>1.24</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -652,14 +648,14 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>mag_castle</t>
+          <t>phy_castle</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1237505</v>
+        <v>1370568</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
@@ -675,29 +671,29 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>mag_castle</t>
+          <t>phy_castle</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1237505</v>
+        <v>1570568</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>45996</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>amelix</t>
+          <t>bobbyf2p</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -706,48 +702,48 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1237505</v>
+        <v>1984824</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.98</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>amelix</t>
+          <t>bobbyf2p</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1570568</v>
+        <v>2984824</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
+        <v>2.98</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>50.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>45995</v>
+        <v>45992</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>amelix</t>
+          <t>bobbyf2p</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -756,25 +752,21 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1570568</v>
+        <v>2543075</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>2.54</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>amelix</t>
+          <t>bobbyf2p</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -783,16 +775,16 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1570568</v>
+        <v>3543075</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="14">
@@ -801,7 +793,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>bobbyf2p</t>
+          <t>exosicz</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -810,10 +802,10 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2984824</v>
+        <v>692347</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
@@ -824,7 +816,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>bobbyf2p</t>
+          <t>exosicz</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -833,52 +825,48 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2984824</v>
+        <v>1692347</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2.98</v>
+        <v>1.69</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0</v>
+        <v>144.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>45996</v>
+        <v>45992</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>bobbyf2p</t>
+          <t>fhzzzzz</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>mag_castle</t>
+          <t>phy_castle</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2984824</v>
+        <v>1218370</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.22</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>bobbyf2p</t>
+          <t>fhzzzzz</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -887,66 +875,66 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3543075</v>
+        <v>1518370</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
+        <v>1.52</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>24.6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>45995</v>
+        <v>45992</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>bobbyf2p</t>
+          <t>hacunamulata</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>3543075</v>
+        <v>1089789</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.09</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>bobbyf2p</t>
+          <t>hacunamulata</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>3543075</v>
+        <v>1189789</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>3.54</v>
+        <v>1.19</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -955,19 +943,19 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>exosicz</t>
+          <t>jjay3o</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>mag_castle</t>
+          <t>phy_castle</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1692347</v>
+        <v>1355555</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr"/>
@@ -978,34 +966,34 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>exosicz</t>
+          <t>jjay3o</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>mag_castle</t>
+          <t>phy_castle</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1692347</v>
+        <v>1555555</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>45996</v>
+        <v>45992</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>exosicz</t>
+          <t>okataxiv</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1014,48 +1002,48 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1692347</v>
+        <v>726637</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>0.73</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>fhzzzzz</t>
+          <t>okataxiv</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1518370</v>
+        <v>1726637</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
+        <v>1.73</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>45995</v>
+        <v>45992</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>fhzzzzz</t>
+          <t>okataxiv</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1064,25 +1052,21 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1518370</v>
+        <v>1315707</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.32</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>fhzzzzz</t>
+          <t>okataxiv</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1091,16 +1075,16 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1518370</v>
+        <v>2315707</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1.52</v>
+        <v>2.32</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="26">
@@ -1109,7 +1093,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>hacunamulata</t>
+          <t>patamonx</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1118,10 +1102,10 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>1189789</v>
+        <v>992866</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1.19</v>
+        <v>0.99</v>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
@@ -1132,7 +1116,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>hacunamulata</t>
+          <t>patamonx</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1141,52 +1125,48 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1189789</v>
+        <v>1992866</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1.19</v>
+        <v>1.99</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>45996</v>
+        <v>45992</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>hacunamulata</t>
+          <t>patamonx</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>mag_castle</t>
+          <t>phy_castle</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1189789</v>
+        <v>1282580</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.28</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>jjay3o</t>
+          <t>patamonx</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1195,66 +1175,66 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1555555</v>
+        <v>1782580</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
+        <v>1.78</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>39.1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>45995</v>
+        <v>45992</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>jjay3o</t>
+          <t>queenzle8</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1555555</v>
+        <v>319895</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>0.32</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>jjay3o</t>
+          <t>queenzle8</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1555555</v>
+        <v>1319895</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="32">
@@ -1263,7 +1243,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>okataxiv</t>
+          <t>saranz1</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1272,10 +1252,10 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1726637</v>
+        <v>1203563</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr"/>
@@ -1286,7 +1266,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>okataxiv</t>
+          <t>saranz1</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1295,25 +1275,25 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1726637</v>
+        <v>1303563</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>45996</v>
+        <v>45992</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>okataxiv</t>
+          <t>susishushi</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1322,48 +1302,48 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1726637</v>
+        <v>1025156</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.03</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>okataxiv</t>
+          <t>susishushi</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>2315707</v>
+        <v>2025156</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
+        <v>2.03</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>97.09999999999999</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>45995</v>
+        <v>45992</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>okataxiv</t>
+          <t>susishushi</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1372,25 +1352,21 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2315707</v>
+        <v>1296249</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>okataxiv</t>
+          <t>susishushi</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -1399,16 +1375,16 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2315707</v>
+        <v>2896249</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0</v>
+        <v>123.1</v>
       </c>
     </row>
     <row r="38">
@@ -1417,19 +1393,19 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>patamonx</t>
+          <t>จารย์บอส</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>mag_castle</t>
+          <t>phy_castle</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1992866</v>
+        <v>1257324</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1.99</v>
+        <v>1.26</v>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr"/>
@@ -1440,34 +1416,34 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>patamonx</t>
+          <t>จารย์บอส</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>mag_castle</t>
+          <t>phy_castle</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1992866</v>
+        <v>1557324</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1.99</v>
+        <v>1.56</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>45996</v>
+        <v>45992</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>patamonx</t>
+          <t>ปู่เสอวน</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1476,555 +1452,39 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1992866</v>
+        <v>1238841</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>1.24</v>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>patamonx</t>
+          <t>ปู่เสอวน</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1782580</v>
+        <v>2738841</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>45995</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>patamonx</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>phy_castle</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>1782580</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>45996</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>patamonx</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>phy_castle</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>1782580</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>queenzle8</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>1319895</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>45995</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>queenzle8</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>1319895</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>45996</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>queenzle8</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>1319895</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>saranz1</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>1303563</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>45995</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>saranz1</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>1303563</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>45996</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>saranz1</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>1303563</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>susishushi</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>2025156</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>45995</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>susishushi</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>2025156</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>45996</v>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>susishushi</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>2025156</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>susishushi</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>phy_castle</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>1896249</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>45995</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>susishushi</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>phy_castle</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>2896249</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>52.6</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
-        <v>45996</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>susishushi</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>phy_castle</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>2896249</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>จารย์บอส</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>phy_castle</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>1557324</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="n">
-        <v>45995</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>จารย์บอส</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>phy_castle</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>1557324</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="n">
-        <v>45996</v>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>จารย์บอส</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>phy_castle</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="n">
-        <v>1557324</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>ปู่เสอวน</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>2738841</v>
-      </c>
-      <c r="E59" s="5" t="n">
         <v>2.74</v>
       </c>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="5" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="n">
-        <v>45995</v>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>ปู่เสอวน</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>2738841</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="n">
-        <v>45996</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>ปู่เสอวน</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>mag_castle</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>2738841</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0</v>
+      <c r="F41" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2108,19 +1568,19 @@
         <v>45992</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>1.37</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="3">
@@ -2138,19 +1598,19 @@
         <v>45992</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2.11</v>
+        <v>1.11</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>2.11</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2161,26 +1621,26 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>mag_castle</t>
+          <t>phy_castle</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>45992</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="5">
@@ -2191,26 +1651,26 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>phy_castle</t>
+          <t>mag_castle</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>45992</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2228,19 +1688,19 @@
         <v>45992</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2.98</v>
+        <v>1.98</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>2.98</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="7">
@@ -2258,19 +1718,19 @@
         <v>45992</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3.54</v>
+        <v>2.54</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>3.54</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="8">
@@ -2288,19 +1748,19 @@
         <v>45992</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>1.69</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>144.9</v>
       </c>
     </row>
     <row r="9">
@@ -2318,19 +1778,19 @@
         <v>45992</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>1.52</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="10">
@@ -2348,19 +1808,19 @@
         <v>45992</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>1.19</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2378,19 +1838,19 @@
         <v>45992</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>1.56</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="12">
@@ -2408,19 +1868,19 @@
         <v>45992</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1.73</v>
+        <v>0.73</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>1.73</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2438,19 +1898,19 @@
         <v>45992</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2.32</v>
+        <v>1.32</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>2.32</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="14">
@@ -2468,19 +1928,19 @@
         <v>45992</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1.99</v>
+        <v>0.99</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>1.99</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -2498,19 +1958,19 @@
         <v>45992</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>1.78</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="16">
@@ -2528,19 +1988,19 @@
         <v>45992</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1.32</v>
+        <v>0.32</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>1.32</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="17">
@@ -2558,19 +2018,19 @@
         <v>45992</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>1.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -2588,19 +2048,19 @@
         <v>45992</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>2.9</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>52.6</v>
+        <v>123.1</v>
       </c>
     </row>
     <row r="19">
@@ -2618,19 +2078,19 @@
         <v>45992</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2.03</v>
+        <v>1.03</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>2.03</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2648,19 +2108,19 @@
         <v>45992</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>1.56</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="21">
@@ -2678,19 +2138,19 @@
         <v>45992</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>2.74</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
